--- a/downloads/Research-Proposal-Canvas.xlsx
+++ b/downloads/Research-Proposal-Canvas.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rf626c2b8ded44603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R7d1d0d9f1fd84c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R28c4e3045c744c2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R6c1908ead1404147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R6774d7e7b1e44057"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="R59945599c1a244e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,7 +346,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Dental Research AI • Free, editable Excel worksheet • Version 2 • 8 September 2026</x:v>
+        <x:v>Dental Research AI • Free editable worksheet • Version 3 • 9 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -383,7 +383,7 @@
         <x:v>1. Read the example</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>Open Completed example. Every study, event, source excerpt, tool record, and action in that sheet is invented for teaching.</x:v>
+        <x:v>Read the Completed example. Published facts are cited to JOP. Proposed plans, practice errors, imagined comments, and AI-use records are labeled teaching exercises; they are not the authors’ original records.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Green = example</x:v>
@@ -444,12 +444,12 @@
         <x:v>Use approved storage</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+    <x:row r="12" ht="150" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Sources / limits</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>Original teaching adaptation. Reporting guidance: https://www.equator-network.org/</x:v>
+        <x:v>Ishiguro D, Omar MS, Lin WS, Nagai T. Journal of Prosthodontics. 2026. Early View; supplied PDF pp. 1–9. Effects of scanner type and prosthesis design–luting protocol combinations on the passive fit of interim implant-supported complete-arch fixed dental prostheses https://onlinelibrary.wiley.com/doi/abs/10.1111/jopr.70218 Methods, PDF pp. 2–5; Tables 1–2, PDF pp. 5–6; limitations, PDF p. 7.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Recheck current guidance</x:v>
@@ -471,7 +471,7 @@
         <x:v>Calculation legend</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>Yellow cells are editable inputs; green cells on the example sheet contain invented entries. Dark teal total rows, if present, contain formulas. Do not replace formulas with typed totals.</x:v>
+        <x:v>Yellow cells are editable; green example cells contain published facts and clearly labeled teaching entries. Dark teal timing totals contain formulas. Preserve formulas when editing.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>No color-only status codes</x:v>
@@ -681,14 +681,14 @@
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Example: laboratory scanner proposal</x:v>
+        <x:v>Example: reconstructing the Ishiguro design</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>COMPLETED EXAMPLE • Entirely hypothetical • Study this example, then complete your own blank sheet.</x:v>
+        <x:v>RETROSPECTIVE TEACHING EXERCISE. Published design facts; proposed timetable and replication decisions are educational.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -714,7 +714,7 @@
         <x:v>Working title</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>Paired laboratory comparison of scanners A and B on manufactured edentulous casts.</x:v>
+        <x:v>Retrospective proposal exercise: scanner and design–luting combinations for interim complete-arch prosthesis fit.</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>Use a descriptive title</x:v>
@@ -725,40 +725,40 @@
         <x:v>Research question</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>How does mean absolute surface deviation from one laboratory reference differ between A and B on the same casts?</x:v>
+        <x:v>In the published master-cast setup, how does binary passive fit vary across two scanners and three design–luting combinations?</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
         <x:v>Population/specimens, comparison, outcome</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="60" customHeight="1">
+    <x:row r="7" ht="69" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>Rationale / evidence gap</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>The team has not completed its evidence search. Comparative background and the evidence gap are TO CONFIRM; no citations are invented.</x:v>
+        <x:v>Ishiguro et al. report workflow-dependent fit in a controlled in vitro setup. A real replication should justify its own evidence gap; this canvas reconstructs the published design for learning.</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
         <x:v>Link verified sources and their limits</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="67" customHeight="1">
+    <x:row r="8" ht="69" customHeight="1">
       <x:c r="A8" s="11" t="str">
         <x:v>Design and experimental unit</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>Paired in vitro study. Each distinct cast receives both devices. Three scans per cast/device are technical repeats, averaged within cast/device; cast is the paired unit.</x:v>
+        <x:v>2 × 3 in vitro study: 60 PMMA prostheses, ten per group, from one cast. Fit is assessed per prosthesis; source-scan mapping is needed to identify dependence across designs.</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
         <x:v>Separate independent units from repeats</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="67" customHeight="1">
+    <x:row r="9" ht="69" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>Eligibility / setting</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>Twelve commercially manufactured edentulous casts are available in one laboratory; one trained operator. Final inclusion and defect rules: TO CONFIRM.</x:v>
+        <x:v>One maxillary edentulous master cast with four parallel MUA analogs. Same splinted assembly scanned extraorally with TRIOS 4 and E4, ten times per device without repositioning.</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>Specify inclusion/exclusion rules</x:v>
@@ -769,73 +769,73 @@
         <x:v>Primary outcome and timing</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Mean absolute surface deviation in µm, measured during the laboratory scan session. Registration region and algorithm settings: TO CONFIRM.</x:v>
+        <x:v>Binary fit/misfit using the reported screw-resistance assessment. This is a laboratory endpoint, not survival or patient comfort.</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>Definition, unit, time point</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="67" customHeight="1">
+    <x:row r="11" ht="69" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>Measurement / bias controls</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Record calibration, reference-system accuracy, scanner order, environment, and masking of analysis where feasible. Final procedures must be specified before collection.</x:v>
+        <x:v>Published initial examiner agreement: 59/60 (98.3%), κ = 0.95. Retain independent ratings and final decisions; record calibration and actual acquisition conditions.</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>Laboratory lead</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="67" customHeight="1">
+    <x:row r="12" ht="69" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Analysis and missing data</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>Proposed B-minus-A contrast of cast/device averages. Statistician must finalize the method, diagnostics, failure handling, and minimum successful repeats before analysis.</x:v>
+        <x:v>Published analysis includes Fisher comparisons. For a replication, prespecify specimen dependence, multiple comparisons, exclusions, and failure handling with a statistician.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Statistician; prespecify decisions</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="67" customHeight="1">
+    <x:row r="13" ht="69" customHeight="1">
       <x:c r="A13" s="11" t="str">
         <x:v>Sample-size justification</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>Twelve available casts is a feasibility constraint. Paired-difference variability, meaningful difference or precision target, and failure allowance are TO CONFIRM.</x:v>
+        <x:v>Published n = 10 per cell is descriptive here. A new protocol needs a meaningful effect or precision target, variance/event assumptions, and failure allowance; observed results are not prospective assumptions.</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>Statistician; justify precision or power</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="67" customHeight="1">
+    <x:row r="14" ht="69" customHeight="1">
       <x:c r="A14" s="11" t="str">
         <x:v>Ethics and consent</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>No patients are proposed. Obtain the applicable institutional determination for manufactured specimens; do not claim an exemption or approval not yet issued.</x:v>
+        <x:v>No new collection in this teaching exercise. A real replication needs the applicable institutional determination for its specimen source; no new approval is claimed.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>Institutional determination</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="67" customHeight="1">
+    <x:row r="15" ht="69" customHeight="1">
       <x:c r="A15" s="11" t="str">
         <x:v>Data management / AI use</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>Read-only raw scans, coded cast/device/repeat keys, versioned processing and analysis scripts. AI input limited to authorized nonconfidential text and invented data; service authorization still pending.</x:v>
+        <x:v>Preserve raw scans, specimen-to-scan mapping, fabrication records, fit ratings, and scripts. AI use in this course does not establish actual AI use by the published authors.</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
         <x:v>Principal investigator / data steward</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="67" customHeight="1">
+    <x:row r="16" ht="69" customHeight="1">
       <x:c r="A16" s="11" t="str">
         <x:v>Feasibility / timetable</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>Proposed 10-week planning/pilot window: weeks 1–2 evidence/protocol; 3–4 calibration/pilot setup; 5–6 pilot scans; 7–8 reproducibility review; 9–10 revised protocol.</x:v>
+        <x:v>Invented eight-week teaching schedule: weeks 1–2 source/protocol; 3–4 measurement/provenance; 5–6 mock analysis; 7–8 reporting review. No new specimens are produced.</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
         <x:v>Project lead; label proposed dates</x:v>
@@ -846,18 +846,18 @@
         <x:v>Sharing and dissemination</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
-        <x:v>Share only cleared code and labeled synthetic examples. Actual scans and unpublished manufacturer specifications are not cleared for public release.</x:v>
+        <x:v>Use original source-cited summaries in teaching. A real project must determine which code, data, and figures may be shared.</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
         <x:v>Confirm rights and permissions</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="60" customHeight="1">
+    <x:row r="18" ht="69" customHeight="1">
       <x:c r="A18" s="11" t="str">
         <x:v>Unresolved decision / owner / due</x:v>
       </x:c>
       <x:c r="B18" s="12" t="str">
-        <x:v>Define primary measurement and sample-size inputs; owners: laboratory lead and statistician; proposed review date: 2026-09-22. Status: TO CONFIRM.</x:v>
+        <x:v>Replication decisions: independent casts, source-scan mapping, objective measurement, and sample size. Proposed roles: laboratory lead/statistician. Review date: TO CONFIRM for any real project.</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
         <x:v>Assign a person and actual due date</x:v>
